--- a/Análisis_Importación_México.xlsx
+++ b/Análisis_Importación_México.xlsx
@@ -1,29 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Semestre 2 - 2026-UAM\3. Tecnologías de Gestión de la Información\Semana 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labcisco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC067762-2317-4838-BA99-DA28C9D7D74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDB3865-78E7-445E-81F5-93C29549ADA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Importación" sheetId="2" r:id="rId1"/>
+    <sheet name="Resultados" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos_Importación!$A$1:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos_Importación!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="128">
   <si>
     <t>No.</t>
   </si>
@@ -383,6 +398,30 @@
   </si>
   <si>
     <t>Organizadores</t>
+  </si>
+  <si>
+    <t>Precio promedio de los productos.</t>
+  </si>
+  <si>
+    <t>Cantidad de productos registrados.</t>
+  </si>
+  <si>
+    <t>Importe correspondiente a los productos de México.</t>
+  </si>
+  <si>
+    <t>1. ¿Cuál es el importe total de la operación?</t>
+  </si>
+  <si>
+    <t>2. ¿Cuál es el producto con mayor import</t>
+  </si>
+  <si>
+    <t>3. ¿Cuál es el precio promedio?</t>
+  </si>
+  <si>
+    <t>4. ¿Cuántos productos están registrados?</t>
+  </si>
+  <si>
+    <t>5. ¿Por qué es importante analizar esta información antes de realizar una operación comercial?</t>
   </si>
 </sst>
 </file>
@@ -441,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -457,6 +496,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,21 +811,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,20 +854,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="2">
@@ -825,23 +876,29 @@
       <c r="G2" s="3">
         <v>4.5</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2" s="3">
+        <f>F2*G2</f>
+        <v>540</v>
+      </c>
+      <c r="I2" s="8" t="str">
+        <f>IF(H2&gt;1000,"Importe Alto","Importe Normal")</f>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="2">
@@ -850,23 +907,29 @@
       <c r="G3" s="3">
         <v>8.75</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H51" si="0">F3*G3</f>
+        <v>743.75</v>
+      </c>
+      <c r="I3" s="8" t="str">
+        <f t="shared" ref="I3:I51" si="1">IF(H3&gt;1000,"Importe Alto","Importe Normal")</f>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2">
@@ -875,23 +938,29 @@
       <c r="G4" s="3">
         <v>3.2</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H4" s="3">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="I4" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2">
@@ -900,23 +969,29 @@
       <c r="G5" s="3">
         <v>2.85</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="2">
@@ -925,23 +1000,29 @@
       <c r="G6" s="3">
         <v>5.4</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H6" s="3">
+        <f t="shared" si="0"/>
+        <v>972.00000000000011</v>
+      </c>
+      <c r="I6" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="2">
@@ -950,23 +1031,29 @@
       <c r="G7" s="3">
         <v>6.8</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H7" s="3">
+        <f t="shared" si="0"/>
+        <v>646</v>
+      </c>
+      <c r="I7" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="2">
@@ -975,23 +1062,29 @@
       <c r="G8" s="3">
         <v>9.5</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H8" s="3">
+        <f t="shared" si="0"/>
+        <v>1045</v>
+      </c>
+      <c r="I8" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="2">
@@ -1000,23 +1093,29 @@
       <c r="G9" s="3">
         <v>3.75</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" s="3">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="I9" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="2">
@@ -1025,23 +1124,29 @@
       <c r="G10" s="3">
         <v>4.25</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H10" s="3">
+        <f t="shared" si="0"/>
+        <v>552.5</v>
+      </c>
+      <c r="I10" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="2">
@@ -1050,23 +1155,29 @@
       <c r="G11" s="3">
         <v>5.6</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="3">
+        <f t="shared" si="0"/>
+        <v>503.99999999999994</v>
+      </c>
+      <c r="I11" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="2">
@@ -1075,23 +1186,29 @@
       <c r="G12" s="3">
         <v>7.25</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="3">
+        <f t="shared" si="0"/>
+        <v>543.75</v>
+      </c>
+      <c r="I12" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="2">
@@ -1100,23 +1217,29 @@
       <c r="G13" s="3">
         <v>2.9</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="3">
+        <f t="shared" si="0"/>
+        <v>638</v>
+      </c>
+      <c r="I13" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="2">
@@ -1125,23 +1248,29 @@
       <c r="G14" s="3">
         <v>2.4</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H14" s="3">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="I14" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="2">
@@ -1150,23 +1279,29 @@
       <c r="G15" s="3">
         <v>3.85</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="3">
+        <f t="shared" si="0"/>
+        <v>539</v>
+      </c>
+      <c r="I15" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="2">
@@ -1175,23 +1310,29 @@
       <c r="G16" s="3">
         <v>4.9000000000000004</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H16" s="3">
+        <f t="shared" si="0"/>
+        <v>490.00000000000006</v>
+      </c>
+      <c r="I16" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="2">
@@ -1200,23 +1341,29 @@
       <c r="G17" s="3">
         <v>3.6</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="3">
+        <f t="shared" si="0"/>
+        <v>648</v>
+      </c>
+      <c r="I17" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="2">
@@ -1225,23 +1372,29 @@
       <c r="G18" s="3">
         <v>3.25</v>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="3">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="I18" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="2">
@@ -1250,23 +1403,29 @@
       <c r="G19" s="3">
         <v>1.8</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="3">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+      <c r="I19" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="2">
@@ -1275,23 +1434,29 @@
       <c r="G20" s="3">
         <v>5.75</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H20" s="3">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="I20" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="2">
@@ -1300,23 +1465,29 @@
       <c r="G21" s="3">
         <v>3.95</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H21" s="3">
+        <f t="shared" si="0"/>
+        <v>493.75</v>
+      </c>
+      <c r="I21" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="2">
@@ -1325,23 +1496,29 @@
       <c r="G22" s="3">
         <v>8.5</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H22" s="3">
+        <f t="shared" si="0"/>
+        <v>765</v>
+      </c>
+      <c r="I22" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="2">
@@ -1350,23 +1527,29 @@
       <c r="G23" s="3">
         <v>4.8</v>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="3">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="I23" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="2">
@@ -1375,23 +1558,29 @@
       <c r="G24" s="3">
         <v>5.25</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H24" s="3">
+        <f t="shared" si="0"/>
+        <v>682.5</v>
+      </c>
+      <c r="I24" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F25" s="2">
@@ -1400,23 +1589,29 @@
       <c r="G25" s="3">
         <v>2.95</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H25" s="3">
+        <f t="shared" si="0"/>
+        <v>531</v>
+      </c>
+      <c r="I25" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="2">
@@ -1425,23 +1620,29 @@
       <c r="G26" s="3">
         <v>7.4</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="3">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="I26" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="2">
@@ -1450,23 +1651,29 @@
       <c r="G27" s="3">
         <v>6.25</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H27" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="I27" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="2">
@@ -1475,23 +1682,29 @@
       <c r="G28" s="3">
         <v>3.5</v>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H28" s="3">
+        <f t="shared" si="0"/>
+        <v>612.5</v>
+      </c>
+      <c r="I28" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="2">
@@ -1500,23 +1713,29 @@
       <c r="G29" s="3">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H29" s="3">
+        <f t="shared" si="0"/>
+        <v>552</v>
+      </c>
+      <c r="I29" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F30" s="2">
@@ -1525,23 +1744,29 @@
       <c r="G30" s="3">
         <v>5.15</v>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="3">
+        <f t="shared" si="0"/>
+        <v>721</v>
+      </c>
+      <c r="I30" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F31" s="2">
@@ -1550,23 +1775,29 @@
       <c r="G31" s="3">
         <v>4.75</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="3">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="I31" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F32" s="2">
@@ -1575,23 +1806,29 @@
       <c r="G32" s="3">
         <v>2.75</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H32" s="3">
+        <f t="shared" si="0"/>
+        <v>687.5</v>
+      </c>
+      <c r="I32" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="2">
@@ -1600,23 +1837,29 @@
       <c r="G33" s="3">
         <v>3.2</v>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H33" s="3">
+        <f t="shared" si="0"/>
+        <v>576</v>
+      </c>
+      <c r="I33" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="2">
@@ -1625,23 +1868,29 @@
       <c r="G34" s="3">
         <v>1.5</v>
       </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H34" s="3">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="I34" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="2">
@@ -1650,23 +1899,29 @@
       <c r="G35" s="3">
         <v>2.9</v>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H35" s="3">
+        <f t="shared" si="0"/>
+        <v>435</v>
+      </c>
+      <c r="I35" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F36" s="2">
@@ -1675,23 +1930,29 @@
       <c r="G36" s="3">
         <v>7.8</v>
       </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H36" s="3">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="I36" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2">
@@ -1700,23 +1961,29 @@
       <c r="G37" s="3">
         <v>12.5</v>
       </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H37" s="3">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="I37" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F38" s="2">
@@ -1725,23 +1992,29 @@
       <c r="G38" s="3">
         <v>11.75</v>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H38" s="3">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="I38" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F39" s="2">
@@ -1750,23 +2023,29 @@
       <c r="G39" s="3">
         <v>15.5</v>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H39" s="3">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="I39" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F40" s="2">
@@ -1775,23 +2054,29 @@
       <c r="G40" s="3">
         <v>13.25</v>
       </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H40" s="3">
+        <f t="shared" si="0"/>
+        <v>993.75</v>
+      </c>
+      <c r="I40" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2">
@@ -1800,23 +2085,29 @@
       <c r="G41" s="3">
         <v>18.5</v>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H41" s="3">
+        <f t="shared" si="0"/>
+        <v>1665</v>
+      </c>
+      <c r="I41" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="2">
@@ -1825,23 +2116,29 @@
       <c r="G42" s="3">
         <v>9.75</v>
       </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="3">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="I42" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="2">
@@ -1850,23 +2147,29 @@
       <c r="G43" s="3">
         <v>7.5</v>
       </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="3">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="I43" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Normal</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="2">
@@ -1875,23 +2178,29 @@
       <c r="G44" s="3">
         <v>22.5</v>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H44" s="3">
+        <f t="shared" si="0"/>
+        <v>1912.5</v>
+      </c>
+      <c r="I44" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2">
@@ -1900,23 +2209,29 @@
       <c r="G45" s="3">
         <v>28</v>
       </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H45" s="3">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="I45" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="9" t="s">
         <v>107</v>
       </c>
       <c r="F46" s="2">
@@ -1925,23 +2240,29 @@
       <c r="G46" s="3">
         <v>8.75</v>
       </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H46" s="3">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="I46" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="9" t="s">
         <v>110</v>
       </c>
       <c r="F47" s="2">
@@ -1950,23 +2271,29 @@
       <c r="G47" s="3">
         <v>12.8</v>
       </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H47" s="3">
+        <f t="shared" si="0"/>
+        <v>1152</v>
+      </c>
+      <c r="I47" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="9" t="s">
         <v>113</v>
       </c>
       <c r="F48" s="2">
@@ -1975,23 +2302,29 @@
       <c r="G48" s="3">
         <v>16.5</v>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H48" s="3">
+        <f t="shared" si="0"/>
+        <v>1237.5</v>
+      </c>
+      <c r="I48" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="2">
@@ -2000,23 +2333,29 @@
       <c r="G49" s="3">
         <v>9.25</v>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H49" s="3">
+        <f t="shared" si="0"/>
+        <v>1017.5</v>
+      </c>
+      <c r="I49" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="2">
@@ -2025,23 +2364,29 @@
       <c r="G50" s="3">
         <v>24.5</v>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H50" s="3">
+        <f t="shared" si="0"/>
+        <v>1592.5</v>
+      </c>
+      <c r="I50" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="9" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="2">
@@ -2050,10 +2395,142 @@
       <c r="G51" s="3">
         <v>10.5</v>
       </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="2"/>
+      <c r="H51" s="3">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="I51" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>Importe Alto</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7">
+        <f>AVERAGE(G2:G51)</f>
+        <v>7.7420000000000009</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6">
+        <f>+COUNTA(A2:A51)</f>
+        <v>50</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6">
+        <f>SUMIF(E2:E51,"México",H2:H51)</f>
+        <v>36919.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D6513E-0E31-4742-A215-F9A6F2AAF74D}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6">
+        <f>+SUM(Datos_Importación!H2:H51)</f>
+        <v>40359</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6">
+        <f>+MAX(Datos_Importación!H2:H51)</f>
+        <v>1912.5</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6">
+        <f>AVERAGE(Datos_Importación!G2:G51)</f>
+        <v>7.7420000000000009</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
+        <f>COUNTA(Datos_Importación!C2:C51)</f>
+        <v>50</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>